--- a/versao final igor.xlsx
+++ b/versao final igor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igor1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/12d55ee7344b40de/Desktop/Projetos/gold/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECCC99F7-11ED-49AA-ACE6-EB4B57B545F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{ECCC99F7-11ED-49AA-ACE6-EB4B57B545F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3688B93F-D2C6-424A-AD64-7EF2D4351E07}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{445FBE18-A1B2-4209-B137-C52DB7416062}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{445FBE18-A1B2-4209-B137-C52DB7416062}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha 1" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,10 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId5"/>
-    <pivotCache cacheId="3" r:id="rId6"/>
-    <pivotCache cacheId="4" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -7762,7 +7761,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{167D5AB4-0AC7-4183-8619-8C9C3F048173}" name="Tabela dinâmica2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{167D5AB4-0AC7-4183-8619-8C9C3F048173}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A1:C5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -7842,7 +7841,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0E10EA0-E89C-4401-BE30-7A8199AB86C8}" name="Tabela dinâmica5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0E10EA0-E89C-4401-BE30-7A8199AB86C8}" name="Tabela dinâmica5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A1:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -7945,7 +7944,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B52C149-84DA-4798-B1B2-DA953C82AA78}" name="Tabela dinâmica7" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B52C149-84DA-4798-B1B2-DA953C82AA78}" name="Tabela dinâmica7" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A1:B13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -8366,6 +8365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68711161-0579-4689-9003-830217C9BFEF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U272"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10161,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>56</v>
       </c>
@@ -10202,7 +10202,7 @@
         <v>2.6999999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>56</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>56</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>22.196999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>56</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>57</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>73.989999999999995</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>57</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>57</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>124.99</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>58</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>59</v>
       </c>
@@ -10530,7 +10530,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>60</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>60</v>
       </c>
@@ -10612,7 +10612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>61</v>
       </c>
@@ -10653,7 +10653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>61</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>61</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>61</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>61</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>61</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>61</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>62</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>62</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>62</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
         <v>62</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
         <v>62</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
         <v>62</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>63</v>
       </c>
@@ -11186,7 +11186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>63</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>63</v>
       </c>
@@ -11268,7 +11268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>64</v>
       </c>
@@ -11309,7 +11309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
         <v>64</v>
       </c>
@@ -11350,7 +11350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
         <v>64</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>64</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>64</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
         <v>64</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>56</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
         <v>56</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>56</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>56</v>
       </c>
@@ -11678,7 +11678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
         <v>65</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
         <v>65</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>65</v>
       </c>
@@ -11801,7 +11801,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>65</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>65</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
         <v>65</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>65</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
         <v>65</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>65</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
         <v>65</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
         <v>65</v>
       </c>
@@ -12129,7 +12129,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
         <v>65</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
         <v>65</v>
       </c>
@@ -12211,7 +12211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
         <v>65</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
         <v>65</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
         <v>65</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
         <v>65</v>
       </c>
@@ -12375,7 +12375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
         <v>65</v>
       </c>
@@ -12416,7 +12416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
         <v>65</v>
       </c>
@@ -12457,7 +12457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
         <v>65</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
         <v>65</v>
       </c>
@@ -12539,7 +12539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
         <v>65</v>
       </c>
@@ -12580,7 +12580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
         <v>65</v>
       </c>
@@ -12621,7 +12621,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
         <v>65</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
         <v>65</v>
       </c>
@@ -12703,7 +12703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
         <v>65</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="s">
         <v>65</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
         <v>65</v>
       </c>
@@ -12826,7 +12826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
         <v>65</v>
       </c>
@@ -12867,7 +12867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
         <v>65</v>
       </c>
@@ -12908,7 +12908,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
         <v>65</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
         <v>65</v>
       </c>
@@ -12990,7 +12990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
         <v>65</v>
       </c>
@@ -13031,7 +13031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
         <v>65</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7" t="s">
         <v>65</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
         <v>65</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7" t="s">
         <v>65</v>
       </c>
@@ -13195,7 +13195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
         <v>65</v>
       </c>
@@ -13236,7 +13236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
         <v>65</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
         <v>58</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
         <v>58</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
         <v>58</v>
       </c>
@@ -13400,7 +13400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
         <v>58</v>
       </c>
@@ -13441,7 +13441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
         <v>58</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="s">
         <v>60</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="s">
         <v>60</v>
       </c>
@@ -13564,7 +13564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
         <v>66</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="7" t="s">
         <v>66</v>
       </c>
@@ -13646,7 +13646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
         <v>66</v>
       </c>
@@ -13687,7 +13687,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="7" t="s">
         <v>66</v>
       </c>
@@ -13728,7 +13728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="7" t="s">
         <v>66</v>
       </c>
@@ -13769,7 +13769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="s">
         <v>66</v>
       </c>
@@ -13810,7 +13810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="7" t="s">
         <v>67</v>
       </c>
@@ -13851,7 +13851,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="7" t="s">
         <v>67</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="s">
         <v>67</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
         <v>67</v>
       </c>
@@ -13974,7 +13974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
         <v>67</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="7" t="s">
         <v>68</v>
       </c>
@@ -14056,7 +14056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="7" t="s">
         <v>68</v>
       </c>
@@ -14097,7 +14097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="s">
         <v>68</v>
       </c>
@@ -14138,7 +14138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="7" t="s">
         <v>68</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="s">
         <v>68</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="7" t="s">
         <v>68</v>
       </c>
@@ -14261,7 +14261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="s">
         <v>69</v>
       </c>
@@ -14302,7 +14302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="7" t="s">
         <v>69</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="s">
         <v>69</v>
       </c>
@@ -14384,7 +14384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="7" t="s">
         <v>69</v>
       </c>
@@ -14425,7 +14425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="7" t="s">
         <v>70</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="7" t="s">
         <v>70</v>
       </c>
@@ -14507,7 +14507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="7" t="s">
         <v>70</v>
       </c>
@@ -14548,7 +14548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="7" t="s">
         <v>70</v>
       </c>
@@ -14589,7 +14589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="7" t="s">
         <v>71</v>
       </c>
@@ -14630,7 +14630,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="7" t="s">
         <v>71</v>
       </c>
@@ -14671,7 +14671,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="7" t="s">
         <v>71</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="7" t="s">
         <v>71</v>
       </c>
@@ -14753,7 +14753,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="s">
         <v>71</v>
       </c>
@@ -14794,7 +14794,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="7" t="s">
         <v>71</v>
       </c>
@@ -14835,7 +14835,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="7" t="s">
         <v>71</v>
       </c>
@@ -14876,7 +14876,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="7" t="s">
         <v>72</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="s">
         <v>72</v>
       </c>
@@ -14958,7 +14958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="7" t="s">
         <v>72</v>
       </c>
@@ -14999,7 +14999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="7" t="s">
         <v>72</v>
       </c>
@@ -15040,7 +15040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="7" t="s">
         <v>72</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="7" t="s">
         <v>72</v>
       </c>
@@ -15122,7 +15122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="7" t="s">
         <v>73</v>
       </c>
@@ -15163,7 +15163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="7" t="s">
         <v>73</v>
       </c>
@@ -15204,7 +15204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="7" t="s">
         <v>73</v>
       </c>
@@ -15245,7 +15245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="s">
         <v>73</v>
       </c>
@@ -15286,7 +15286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="7" t="s">
         <v>74</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="7" t="s">
         <v>74</v>
       </c>
@@ -15368,7 +15368,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="7" t="s">
         <v>74</v>
       </c>
@@ -15409,7 +15409,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="7" t="s">
         <v>74</v>
       </c>
@@ -15450,7 +15450,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="7" t="s">
         <v>74</v>
       </c>
@@ -15491,7 +15491,7 @@
         <v>99.99</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="7" t="s">
         <v>75</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>69.989999999999995</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="7" t="s">
         <v>75</v>
       </c>
@@ -15573,7 +15573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="7" t="s">
         <v>75</v>
       </c>
@@ -15614,7 +15614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="7" t="s">
         <v>75</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="7" t="s">
         <v>76</v>
       </c>
@@ -15696,7 +15696,7 @@
         <v>72.989999999999995</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="7" t="s">
         <v>76</v>
       </c>
@@ -15737,7 +15737,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="7" t="s">
         <v>76</v>
       </c>
@@ -15778,7 +15778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="7" t="s">
         <v>76</v>
       </c>
@@ -15819,7 +15819,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="7" t="s">
         <v>77</v>
       </c>
@@ -15860,7 +15860,7 @@
         <v>110.98499999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="7" t="s">
         <v>77</v>
       </c>
@@ -15901,7 +15901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="7" t="s">
         <v>78</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>110.98499999999999</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="7" t="s">
         <v>78</v>
       </c>
@@ -15983,7 +15983,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="7" t="s">
         <v>79</v>
       </c>
@@ -16024,7 +16024,7 @@
         <v>149.98499999999999</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="7" t="s">
         <v>79</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>149.98499999999999</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="7" t="s">
         <v>80</v>
       </c>
@@ -16106,7 +16106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="7" t="s">
         <v>81</v>
       </c>
@@ -16147,7 +16147,7 @@
         <v>119.98499999999999</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="7" t="s">
         <v>78</v>
       </c>
@@ -16188,7 +16188,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="7" t="s">
         <v>78</v>
       </c>
@@ -16229,7 +16229,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="7" t="s">
         <v>78</v>
       </c>
@@ -16270,7 +16270,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="7" t="s">
         <v>78</v>
       </c>
@@ -16311,7 +16311,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="7" t="s">
         <v>78</v>
       </c>
@@ -16352,7 +16352,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="7" t="s">
         <v>78</v>
       </c>
@@ -16393,7 +16393,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="7" t="s">
         <v>78</v>
       </c>
@@ -16434,7 +16434,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="7" t="s">
         <v>78</v>
       </c>
@@ -16475,7 +16475,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="7" t="s">
         <v>78</v>
       </c>
@@ -16516,7 +16516,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="7" t="s">
         <v>78</v>
       </c>
@@ -16557,7 +16557,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="7" t="s">
         <v>78</v>
       </c>
@@ -16598,7 +16598,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="7" t="s">
         <v>78</v>
       </c>
@@ -16639,7 +16639,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>78</v>
       </c>
@@ -16680,7 +16680,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>78</v>
       </c>
@@ -16721,7 +16721,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="s">
         <v>78</v>
       </c>
@@ -16762,7 +16762,7 @@
         <v>59.984999999999999</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="s">
         <v>81</v>
       </c>
@@ -16803,7 +16803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="s">
         <v>79</v>
       </c>
@@ -16844,7 +16844,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="s">
         <v>79</v>
       </c>
@@ -16885,7 +16885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="s">
         <v>79</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="7" t="s">
         <v>79</v>
       </c>
@@ -16967,7 +16967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="7" t="s">
         <v>79</v>
       </c>
@@ -17008,7 +17008,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
         <v>79</v>
       </c>
@@ -17049,7 +17049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="7" t="s">
         <v>79</v>
       </c>
@@ -17090,7 +17090,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="7" t="s">
         <v>82</v>
       </c>
@@ -17131,7 +17131,7 @@
         <v>149.98499999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="7" t="s">
         <v>82</v>
       </c>
@@ -17172,7 +17172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="7" t="s">
         <v>82</v>
       </c>
@@ -17213,7 +17213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="7" t="s">
         <v>82</v>
       </c>
@@ -17254,7 +17254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="7" t="s">
         <v>82</v>
       </c>
@@ -17295,7 +17295,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="7" t="s">
         <v>82</v>
       </c>
@@ -17336,7 +17336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="7" t="s">
         <v>82</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="7" t="s">
         <v>82</v>
       </c>
@@ -17418,7 +17418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="7" t="s">
         <v>82</v>
       </c>
@@ -17459,7 +17459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="7" t="s">
         <v>82</v>
       </c>
@@ -17500,7 +17500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="7" t="s">
         <v>82</v>
       </c>
@@ -17541,7 +17541,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="7" t="s">
         <v>82</v>
       </c>
@@ -17582,7 +17582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="7" t="s">
         <v>82</v>
       </c>
@@ -17623,7 +17623,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="7" t="s">
         <v>82</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="7" t="s">
         <v>83</v>
       </c>
@@ -17705,7 +17705,7 @@
         <v>149.98499999999999</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="7" t="s">
         <v>83</v>
       </c>
@@ -17746,7 +17746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="7" t="s">
         <v>83</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="7" t="s">
         <v>83</v>
       </c>
@@ -17828,7 +17828,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="7" t="s">
         <v>83</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="7" t="s">
         <v>83</v>
       </c>
@@ -17910,7 +17910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="7" t="s">
         <v>83</v>
       </c>
@@ -17951,7 +17951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="7" t="s">
         <v>83</v>
       </c>
@@ -17992,7 +17992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="7" t="s">
         <v>83</v>
       </c>
@@ -18033,7 +18033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="7" t="s">
         <v>83</v>
       </c>
@@ -18074,7 +18074,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="7" t="s">
         <v>83</v>
       </c>
@@ -18115,7 +18115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="7" t="s">
         <v>83</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="7" t="s">
         <v>83</v>
       </c>
@@ -18197,7 +18197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
         <v>83</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="7" t="s">
         <v>83</v>
       </c>
@@ -18279,7 +18279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
         <v>83</v>
       </c>
@@ -18320,7 +18320,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
         <v>83</v>
       </c>
@@ -18361,7 +18361,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="7" t="s">
         <v>83</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="7" t="s">
         <v>83</v>
       </c>
@@ -18443,7 +18443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="7" t="s">
         <v>84</v>
       </c>
@@ -18484,7 +18484,7 @@
         <v>149.98499999999999</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="7" t="s">
         <v>84</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="7" t="s">
         <v>84</v>
       </c>
@@ -18566,7 +18566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="7" t="s">
         <v>84</v>
       </c>
@@ -18607,7 +18607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="7" t="s">
         <v>84</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="7" t="s">
         <v>84</v>
       </c>
@@ -18689,7 +18689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="7" t="s">
         <v>85</v>
       </c>
@@ -18730,7 +18730,7 @@
         <v>149.98499999999999</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="7" t="s">
         <v>85</v>
       </c>
@@ -18771,7 +18771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="7" t="s">
         <v>85</v>
       </c>
@@ -18812,7 +18812,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="7" t="s">
         <v>85</v>
       </c>
@@ -18853,7 +18853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="7" t="s">
         <v>80</v>
       </c>
@@ -18894,7 +18894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="7" t="s">
         <v>80</v>
       </c>
@@ -18935,7 +18935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="7" t="s">
         <v>80</v>
       </c>
@@ -18976,7 +18976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="7" t="s">
         <v>80</v>
       </c>
@@ -19017,7 +19017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="7" t="s">
         <v>81</v>
       </c>
@@ -19058,7 +19058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="7" t="s">
         <v>81</v>
       </c>
@@ -19099,7 +19099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="7" t="s">
         <v>81</v>
       </c>
@@ -19140,7 +19140,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="7" t="s">
         <v>86</v>
       </c>
@@ -19181,7 +19181,7 @@
         <v>82.484999999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="7" t="s">
         <v>86</v>
       </c>
@@ -19222,7 +19222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="7" t="s">
         <v>86</v>
       </c>
@@ -19263,7 +19263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="7" t="s">
         <v>87</v>
       </c>
@@ -19304,7 +19304,7 @@
         <v>149.98499999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="7" t="s">
         <v>87</v>
       </c>
@@ -19345,7 +19345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="7" t="s">
         <v>87</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="7" t="s">
         <v>87</v>
       </c>
@@ -19427,7 +19427,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="7" t="s">
         <v>77</v>
       </c>
@@ -19468,7 +19468,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="7" t="s">
         <v>88</v>
       </c>
@@ -19509,7 +19509,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="7" t="s">
         <v>89</v>
       </c>
@@ -19548,7 +19548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="7" t="s">
         <v>88</v>
       </c>
@@ -19589,7 +19589,7 @@
         <v>63.99</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="7" t="s">
         <v>88</v>
       </c>
@@ -19630,7 +19630,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="7" t="s">
         <v>90</v>
       </c>
@@ -19671,7 +19671,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="7" t="s">
         <v>78</v>
       </c>
@@ -19712,7 +19712,7 @@
         <v>718.5</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="7" t="s">
         <v>78</v>
       </c>
@@ -19754,7 +19754,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F272" xr:uid="{68711161-0579-4689-9003-830217C9BFEF}"/>
+  <autoFilter ref="A1:F272" xr:uid="{68711161-0579-4689-9003-830217C9BFEF}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="CONSULTOR 3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
